--- a/eznlp/sequence_tagging/transition.xlsx
+++ b/eznlp/sequence_tagging/transition.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="BIO1" sheetId="5" r:id="rId1"/>
     <sheet name="BIO2" sheetId="1" r:id="rId2"/>
     <sheet name="BIOES" sheetId="4" r:id="rId3"/>
+    <sheet name="OntoNotes" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="29">
   <si>
     <t>from_tag</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,6 +90,42 @@
   </si>
   <si>
     <t>start_of_chunk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(*</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -600,13 +637,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="10.625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="15.625" style="1" customWidth="1"/>
+    <col min="1" max="3" width="10.6328125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -623,7 +660,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -640,7 +677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -657,7 +694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -674,7 +711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -691,7 +728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -708,7 +745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -725,7 +762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -742,7 +779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -759,7 +796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
@@ -776,7 +813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.25" thickTop="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -787,17 +824,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="10.625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="15.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="1" max="3" width="10.6328125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6328125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="15.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.6328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -835,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -873,7 +910,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -911,7 +948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -949,7 +986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -987,7 +1024,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1025,7 +1062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -1063,7 +1100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1101,7 +1138,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -1139,7 +1176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
@@ -1177,7 +1214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1188,17 +1225,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="10.625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="15.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="15.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="1" max="3" width="10.6328125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6328125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="15.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.6328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1236,7 +1273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -1274,7 +1311,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
@@ -1312,7 +1349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -1350,7 +1387,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
@@ -1388,7 +1425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
@@ -1426,7 +1463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1464,7 +1501,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -1502,7 +1539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1540,7 +1577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1578,7 +1615,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
@@ -1616,7 +1653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -1654,7 +1691,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
@@ -1692,7 +1729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
@@ -1730,7 +1767,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
@@ -1768,7 +1805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>17</v>
       </c>
@@ -1806,7 +1843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -1844,7 +1881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
@@ -1882,7 +1919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
@@ -1920,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>16</v>
       </c>
@@ -1958,7 +1995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>17</v>
       </c>
@@ -1996,7 +2033,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
@@ -2034,7 +2071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>14</v>
       </c>
@@ -2072,7 +2109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
@@ -2110,7 +2147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>16</v>
       </c>
@@ -2148,7 +2185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>17</v>
       </c>
@@ -2186,10 +2223,316 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="14.25" thickTop="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:12" ht="14.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="10.6328125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.6328125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="14.5" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
 </file>